--- a/docs/downloads/经营分_河南省区__郑州北片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__郑州北片区_2026-10-18.xlsx
@@ -1474,38 +1474,38 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>焦作市</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6732039711952586766</t>
+          <t>7071088733952411655</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>麗枫酒店（郑州T10探十里陇海西路地铁站店）</t>
+          <t>白玉兰酒店(焦作高铁站远大未来城店)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>麗枫酒店(郑州T10探十里陇海西路店)</t>
+          <t>白玉兰商务酒店(焦作远大未来城高铁站店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1515,13 +1515,13 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
@@ -1567,17 +1567,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6601180923536869384</t>
+          <t>7255964066311571467</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7天优品Premium（焦作火车站建设路店）</t>
+          <t>7天酒店（新7天焦作沁阳店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7天优品Premium(焦作火车站建设路店)</t>
+          <t>7天酒店.焦作沁阳店</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I12" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1603,13 +1603,13 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
@@ -1650,22 +1650,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>焦作市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7071088733952411655</t>
+          <t>7045105846606546958</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>白玉兰酒店(焦作高铁站远大未来城店)</t>
+          <t>锦江之星品尚(郑州中学冬青街地铁站瑞达路酒店)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店(焦作远大未来城高铁站店)</t>
+          <t>锦江之星品尚(郑州中学瑞达路酒店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1674,14 +1674,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I13" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1691,13 +1691,13 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
@@ -1738,27 +1738,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>焦作市</t>
+          <t>三门峡市</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7255964066311571467</t>
+          <t>7516463117560186914</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7天酒店（新7天焦作沁阳店）</t>
+          <t>锦江之星（三门峡灵宝物华路天基广场店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7天酒店.焦作沁阳店</t>
+          <t>锦江之星(三门峡灵宝物华路天基广场店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1779,13 +1779,13 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
       </c>
       <c r="O14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
         <v>30</v>
@@ -1831,29 +1831,29 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7045105846606546958</t>
+          <t>6732039711952586766</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>锦江之星品尚(郑州中学冬青街地铁站瑞达路酒店)</t>
+          <t>麗枫酒店（郑州T10探十里陇海西路地铁站店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>锦江之星品尚(郑州中学瑞达路酒店)</t>
+          <t>麗枫酒店(郑州T10探十里陇海西路店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>92</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1873,13 +1873,13 @@
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1914,31 +1914,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>三门峡市</t>
+          <t>焦作市</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7516463117560186914</t>
+          <t>6601180923536869384</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>锦江之星（三门峡灵宝物华路天基广场店）</t>
+          <t>7天优品Premium（焦作火车站建设路店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>锦江之星(三门峡灵宝物华路天基广场店)</t>
+          <t>7天优品Premium(焦作火车站建设路店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
@@ -2029,7 +2029,7 @@
         <v>95</v>
       </c>
       <c r="I17" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2970,38 +2970,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>三门峡市</t>
+          <t>焦作市</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7279409078169536548</t>
+          <t>6872818322086332423</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7天酒店（三门峡灵宝长安路店）</t>
+          <t>麗枫酒店（焦作万方桥高铁站店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7天酒店(三门峡灵宝长安路店)</t>
+          <t>麗枫酒店(焦作万方桥高铁站店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I28" t="n">
         <v>-5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3011,7 +3011,7 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
@@ -3023,7 +3023,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3058,38 +3058,38 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>焦作市</t>
+          <t>三门峡市</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7472636189512108044</t>
+          <t>7279409078169536548</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7天酒店（焦作高铁站店）</t>
+          <t>7天酒店（三门峡灵宝长安路店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>7天酒店(焦作高铁站店)</t>
+          <t>7天酒店(三门峡灵宝长安路店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>110</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3105,13 +3105,13 @@
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3151,17 +3151,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7025615068775581727</t>
+          <t>7472636189512108044</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IU酒店（焦作孟州会昌路店）</t>
+          <t>7天酒店（焦作高铁站店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>iu酒店(孟州中心店)</t>
+          <t>7天酒店(焦作高铁站店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3234,22 +3234,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>三门峡市</t>
+          <t>焦作市</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7328335856194816019</t>
+          <t>7025615068775581727</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（三门峡灵宝函谷路市府店）</t>
+          <t>IU酒店（焦作孟州会昌路店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(三门峡灵宝函谷路市府店)</t>
+          <t>iu酒店(孟州中心店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3322,22 +3322,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>三门峡市</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>7209853572169599028</t>
+          <t>7328335856194816019</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（郑州巩义市政府商学院店）</t>
+          <t>维也纳国际酒店（三门峡灵宝函谷路市府店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(巩义市政府商学院店)</t>
+          <t>维也纳国际酒店(三门峡灵宝函谷路市府店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3363,13 +3363,13 @@
         <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N32" t="n">
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>焦作市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>7478167359174215730</t>
+          <t>7209853572169599028</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>锦江之星（焦作大学师专太极体育中心店）</t>
+          <t>维也纳智好酒店（郑州巩义市政府商学院店）</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>锦江之星(焦作大学师专太极体育中心店)</t>
+          <t>维也纳智好酒店(巩义市政府商学院店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3498,27 +3498,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>焦作市</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>7457801515613292598</t>
+          <t>7478167359174215730</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>锦江之星（郑州荥阳新区店）</t>
+          <t>锦江之星（焦作大学师专太极体育中心店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>锦江之星(荥阳新区店)</t>
+          <t>锦江之星(焦作大学师专太极体育中心店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -3539,13 +3539,13 @@
         <v>10</v>
       </c>
       <c r="M34" t="n">
+        <v>30</v>
+      </c>
+      <c r="N34" t="n">
+        <v>30</v>
+      </c>
+      <c r="O34" t="n">
         <v>25</v>
-      </c>
-      <c r="N34" t="n">
-        <v>30</v>
-      </c>
-      <c r="O34" t="n">
-        <v>30</v>
       </c>
       <c r="P34" t="n">
         <v>30</v>
@@ -3586,27 +3586,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>焦作市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>6872818322086332423</t>
+          <t>7457801515613292598</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>麗枫酒店（焦作万方桥高铁站店）</t>
+          <t>锦江之星（郑州荥阳新区店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>麗枫酒店(焦作万方桥高铁站店)</t>
+          <t>锦江之星(荥阳新区店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3627,7 +3627,7 @@
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N35" t="n">
         <v>30</v>
@@ -3639,7 +3639,7 @@
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
